--- a/filer/24137414_spies.xlsx
+++ b/filer/24137414_spies.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/10–30/9 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/24137414_spies.xlsx
+++ b/filer/24137414_spies.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +644,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1498,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2592,35 +2592,35 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
@@ -3686,19 +3686,19 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
@@ -3804,19 +3804,19 @@
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="75" ht="16" customHeight="1">
@@ -4114,6 +4114,13 @@
       <c r="F85" s="13">
         <f>IFERROR($F$32/($F$53+0)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4145,19 +4152,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4167,19 +4174,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>661135</v>
+        <v>618509</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>618509</v>
+        <v>1757606</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1757606</v>
+        <v>1887988</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>1887988</v>
+        <v>1984026</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>1984026</v>
+        <v>2067544</v>
       </c>
     </row>
     <row r="3">
@@ -4188,18 +4195,20 @@
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
+      <c r="B3" s="16" t="n">
+        <v>35126</v>
+      </c>
       <c r="C3" s="16" t="n">
-        <v>35126</v>
+        <v>5572</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>5572</v>
+        <v>13660</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>13660</v>
+        <v>15422</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>15422</v>
+        <v>16213</v>
       </c>
     </row>
     <row r="4">
@@ -4220,18 +4229,20 @@
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
+      <c r="B5" s="16" t="n">
+        <v>674413</v>
+      </c>
       <c r="C5" s="16" t="n">
-        <v>674413</v>
+        <v>1681535</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>1681535</v>
+        <v>1847897</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>1847897</v>
+        <v>1920192</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>1920192</v>
+        <v>2018134</v>
       </c>
     </row>
     <row r="6">
@@ -4240,18 +4251,20 @@
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
+      <c r="B6" s="16" t="n">
+        <v>-20778</v>
+      </c>
       <c r="C6" s="16" t="n">
-        <v>-20778</v>
+        <v>81643</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>81643</v>
+        <v>53751</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>53751</v>
+        <v>79256</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>79256</v>
+        <v>65623</v>
       </c>
     </row>
     <row r="7">
@@ -4260,18 +4273,20 @@
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
+      <c r="B7" s="16" t="n">
+        <v>26903</v>
+      </c>
       <c r="C7" s="16" t="n">
-        <v>26903</v>
+        <v>33286</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>33286</v>
+        <v>40415</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>40415</v>
+        <v>41815</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>41815</v>
+        <v>40128</v>
       </c>
     </row>
     <row r="8">
@@ -4287,7 +4302,9 @@
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
+      <c r="B9" s="16" t="n">
+        <v>34</v>
+      </c>
       <c r="C9" s="16" t="n">
         <v>34</v>
       </c>
@@ -4295,10 +4312,10 @@
         <v>34</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>29</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10">
@@ -4311,7 +4328,9 @@
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="F10" s="16" t="n">
+        <v>631</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
@@ -4320,19 +4339,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>-53638</v>
+        <v>-47715</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-47715</v>
+        <v>48323</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>48323</v>
+        <v>13302</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>13302</v>
+        <v>37412</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>37412</v>
+        <v>24514</v>
       </c>
     </row>
     <row r="12">
@@ -4356,9 +4375,11 @@
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="16" t="n"/>
       <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
+      <c r="E13" s="16" t="n">
+        <v>20273</v>
+      </c>
       <c r="F13" s="16" t="n">
-        <v>20273</v>
+        <v>57340</v>
       </c>
     </row>
     <row r="14">
@@ -4367,18 +4388,20 @@
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
+      <c r="B14" s="16" t="n">
+        <v>10268</v>
+      </c>
       <c r="C14" s="16" t="n">
-        <v>10268</v>
+        <v>15703</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>15703</v>
+        <v>19032</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>19032</v>
+        <v>32261</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>32261</v>
+        <v>57779</v>
       </c>
     </row>
     <row r="15">
@@ -4388,14 +4411,12 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>-9311</v>
+        <v>-10268</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>-10268</v>
-      </c>
-      <c r="D15" s="16" t="n">
         <v>-15703</v>
       </c>
+      <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
     </row>
@@ -4405,18 +4426,20 @@
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
+      <c r="B16" s="16" t="n">
+        <v>-57983</v>
+      </c>
       <c r="C16" s="16" t="n">
-        <v>-57983</v>
+        <v>32620</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>32620</v>
+        <v>-5730</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-5730</v>
+        <v>25424</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>25424</v>
+        <v>24075</v>
       </c>
     </row>
     <row r="17">
@@ -4425,18 +4448,20 @@
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
+      <c r="B17" s="16" t="n">
+        <v>-11760</v>
+      </c>
       <c r="C17" s="16" t="n">
-        <v>-11760</v>
+        <v>-9566</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>-9566</v>
+        <v>2582</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>2582</v>
+        <v>7380</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>7380</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="18">
@@ -4446,19 +4471,19 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>-49127</v>
+        <v>-46223</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>-46223</v>
+        <v>42186</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>42186</v>
+        <v>-8312</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>-8312</v>
+        <v>18044</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>18044</v>
+        <v>18885</v>
       </c>
     </row>
     <row r="19">
@@ -4468,19 +4493,19 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -4490,17 +4515,17 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>-158</v>
+        <v>0</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n">
+        <v>386</v>
+      </c>
       <c r="F20" s="16" t="n">
-        <v>386</v>
+        <v>1366</v>
       </c>
     </row>
   </sheetData>
@@ -4532,19 +4557,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4577,7 +4602,9 @@
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
+      <c r="B4" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" s="16" t="n">
         <v>0</v>
       </c>
@@ -4585,10 +4612,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>380</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="5">
@@ -4597,15 +4624,17 @@
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
+      <c r="B5" s="16" t="n">
+        <v>90</v>
+      </c>
       <c r="C5" s="16" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>0</v>
@@ -4629,18 +4658,20 @@
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
+      <c r="B7" s="16" t="n">
+        <v>90</v>
+      </c>
       <c r="C7" s="16" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>22</v>
+        <v>380</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>380</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="8">
@@ -4661,18 +4692,20 @@
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
+      <c r="B9" s="16" t="n">
+        <v>807</v>
+      </c>
       <c r="C9" s="16" t="n">
-        <v>807</v>
+        <v>853</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>853</v>
+        <v>917</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>917</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>917</v>
+        <v>737</v>
       </c>
     </row>
     <row r="10">
@@ -4681,18 +4714,20 @@
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
+      <c r="B10" s="16" t="n">
+        <v>807</v>
+      </c>
       <c r="C10" s="16" t="n">
-        <v>807</v>
+        <v>853</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>853</v>
+        <v>917</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>917</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>917</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11">
@@ -4701,18 +4736,20 @@
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
+      <c r="B11" s="16" t="n">
+        <v>897</v>
+      </c>
       <c r="C11" s="16" t="n">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>909</v>
+        <v>939</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>939</v>
+        <v>1297</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>1297</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="12">
@@ -4721,18 +4758,20 @@
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
+      <c r="B12" s="16" t="n">
+        <v>27661</v>
+      </c>
       <c r="C12" s="16" t="n">
-        <v>27661</v>
+        <v>22436</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>22436</v>
+        <v>29587</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>29587</v>
+        <v>41927</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>41927</v>
+        <v>41053</v>
       </c>
     </row>
     <row r="13">
@@ -4741,18 +4780,20 @@
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
+      <c r="B13" s="16" t="n">
+        <v>331912</v>
+      </c>
       <c r="C13" s="16" t="n">
-        <v>331912</v>
+        <v>310627</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>310627</v>
+        <v>238464</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>238464</v>
+        <v>263685</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>263685</v>
+        <v>349987</v>
       </c>
     </row>
     <row r="14">
@@ -4761,18 +4802,20 @@
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
+      <c r="B14" s="16" t="n">
+        <v>226</v>
+      </c>
       <c r="C14" s="16" t="n">
-        <v>226</v>
+        <v>4991</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>4991</v>
+        <v>1288</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>1288</v>
+        <v>6788</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>6788</v>
+        <v>11912</v>
       </c>
     </row>
     <row r="15">
@@ -4781,18 +4824,20 @@
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
+      <c r="B15" s="16" t="n">
+        <v>714</v>
+      </c>
       <c r="C15" s="16" t="n">
-        <v>714</v>
+        <v>1263</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1263</v>
+        <v>2862</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>2862</v>
+        <v>9274</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>9274</v>
+        <v>25479</v>
       </c>
     </row>
     <row r="16">
@@ -4801,18 +4846,20 @@
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n"/>
+      <c r="B16" s="16" t="n">
+        <v>26212</v>
+      </c>
       <c r="C16" s="16" t="n">
-        <v>26212</v>
+        <v>24826</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>24826</v>
+        <v>15084</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>15084</v>
+        <v>10623</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>10623</v>
+        <v>7361</v>
       </c>
     </row>
     <row r="17">
@@ -4845,18 +4892,20 @@
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
+      <c r="B19" s="16" t="n">
+        <v>386725</v>
+      </c>
       <c r="C19" s="16" t="n">
-        <v>386725</v>
+        <v>364143</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>364143</v>
+        <v>287285</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>287285</v>
+        <v>332297</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>332297</v>
+        <v>435792</v>
       </c>
     </row>
     <row r="20">
@@ -4877,18 +4926,20 @@
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
+      <c r="B21" s="16" t="n">
+        <v>47700</v>
+      </c>
       <c r="C21" s="16" t="n">
-        <v>47700</v>
+        <v>134700</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>134700</v>
+        <v>135700</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>135700</v>
+        <v>185700</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>185700</v>
+        <v>103700</v>
       </c>
     </row>
     <row r="22">
@@ -4897,18 +4948,20 @@
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
+      <c r="B22" s="16" t="n">
+        <v>434425</v>
+      </c>
       <c r="C22" s="16" t="n">
-        <v>434425</v>
+        <v>498843</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>498843</v>
+        <v>422985</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>422985</v>
+        <v>517997</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>517997</v>
+        <v>539492</v>
       </c>
     </row>
     <row r="23">
@@ -4918,19 +4971,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>62017</v>
+        <v>435322</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>435322</v>
+        <v>499752</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>499752</v>
+        <v>423924</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>423924</v>
+        <v>519294</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>519294</v>
+        <v>541625</v>
       </c>
     </row>
     <row r="24">
@@ -4939,7 +4992,9 @@
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
+      <c r="B24" s="16" t="n">
+        <v>36000</v>
+      </c>
       <c r="C24" s="16" t="n">
         <v>36000</v>
       </c>
@@ -5007,18 +5062,20 @@
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
+      <c r="B29" s="16" t="n">
+        <v>-8823</v>
+      </c>
       <c r="C29" s="16" t="n">
-        <v>-8823</v>
+        <v>3363</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>3363</v>
+        <v>-4949</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>-4949</v>
+        <v>13095</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>13095</v>
+        <v>31980</v>
       </c>
     </row>
     <row r="30">
@@ -5028,19 +5085,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>-126600</v>
+        <v>27177</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>27177</v>
+        <v>69363</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>69363</v>
+        <v>31051</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>31051</v>
+        <v>49095</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>49095</v>
+        <v>67980</v>
       </c>
     </row>
     <row r="31">
@@ -5049,12 +5106,14 @@
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
+      <c r="B31" s="16" t="n">
+        <v>642</v>
+      </c>
       <c r="C31" s="16" t="n">
         <v>642</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>642</v>
+        <v>800</v>
       </c>
       <c r="E31" s="16" t="n">
         <v>800</v>
@@ -5117,18 +5176,20 @@
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n"/>
+      <c r="B36" s="16" t="n">
+        <v>6109</v>
+      </c>
       <c r="C36" s="16" t="n">
-        <v>6109</v>
+        <v>4519</v>
       </c>
       <c r="D36" s="16" t="n">
-        <v>4519</v>
+        <v>7269</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>7269</v>
+        <v>2603</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>2603</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="37">
@@ -5137,18 +5198,20 @@
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
+      <c r="B37" s="16" t="n">
+        <v>73597</v>
+      </c>
       <c r="C37" s="16" t="n">
-        <v>73597</v>
+        <v>115346</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>115346</v>
+        <v>51154</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>51154</v>
+        <v>99542</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>99542</v>
+        <v>61792</v>
       </c>
     </row>
     <row r="38">
@@ -5169,13 +5232,13 @@
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
+      <c r="B39" s="16" t="n">
+        <v>17464</v>
+      </c>
       <c r="C39" s="16" t="n">
-        <v>17464</v>
-      </c>
-      <c r="D39" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D39" s="16" t="n"/>
       <c r="E39" s="16" t="n"/>
       <c r="F39" s="16" t="n"/>
     </row>
@@ -5185,18 +5248,20 @@
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
+      <c r="B40" s="16" t="n">
+        <v>631</v>
+      </c>
       <c r="C40" s="16" t="n">
-        <v>631</v>
+        <v>7160</v>
       </c>
       <c r="D40" s="16" t="n">
-        <v>7160</v>
+        <v>0</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>0</v>
+        <v>2919</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>2919</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="41">
@@ -5205,18 +5270,20 @@
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
+      <c r="B41" s="16" t="n">
+        <v>8302</v>
+      </c>
       <c r="C41" s="16" t="n">
-        <v>8302</v>
+        <v>7067</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>7067</v>
+        <v>5247</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>5247</v>
+        <v>4309</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>4309</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="42">
@@ -5225,18 +5292,20 @@
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
+      <c r="B42" s="16" t="n">
+        <v>301400</v>
+      </c>
       <c r="C42" s="16" t="n">
-        <v>301400</v>
+        <v>295655</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>295655</v>
+        <v>328403</v>
       </c>
       <c r="E42" s="16" t="n">
-        <v>328403</v>
+        <v>360026</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>360026</v>
+        <v>398764</v>
       </c>
     </row>
     <row r="43">
@@ -5245,18 +5314,20 @@
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
+      <c r="B43" s="16" t="n">
+        <v>407503</v>
+      </c>
       <c r="C43" s="16" t="n">
-        <v>407503</v>
+        <v>429747</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>429747</v>
+        <v>392073</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>392073</v>
+        <v>469399</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>469399</v>
+        <v>472845</v>
       </c>
     </row>
     <row r="44">
@@ -5265,18 +5336,20 @@
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
+      <c r="B44" s="16" t="n">
+        <v>407503</v>
+      </c>
       <c r="C44" s="16" t="n">
-        <v>407503</v>
+        <v>429747</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>429747</v>
+        <v>392073</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>392073</v>
+        <v>469399</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>469399</v>
+        <v>472845</v>
       </c>
     </row>
     <row r="45">
@@ -5286,19 +5359,19 @@
         </is>
       </c>
       <c r="B45" s="16" t="n">
-        <v>62017</v>
+        <v>435322</v>
       </c>
       <c r="C45" s="16" t="n">
-        <v>435322</v>
+        <v>499752</v>
       </c>
       <c r="D45" s="16" t="n">
-        <v>499752</v>
+        <v>423924</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>423924</v>
+        <v>519294</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>519294</v>
+        <v>541625</v>
       </c>
     </row>
   </sheetData>
@@ -5337,13 +5410,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6048,7 +6121,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6166,7 +6239,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -6342,7 +6415,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
